--- a/output/pdf_financials_xlsx/MATA.xlsx
+++ b/output/pdf_financials_xlsx/MATA.xlsx
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.026735</v>
+        <v>-0.026735</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.195127</v>
+        <v>-0.195127</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.026735</v>
+        <v>-0.026735</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.195127</v>
+        <v>-0.195127</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         <v>-0.015612</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.026735</v>
+        <v>-0.026735</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.195127</v>
+        <v>-0.195127</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.026735</v>
+        <v>-0.026735</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.195127</v>
+        <v>-0.195127</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.026735</v>
+        <v>-0.026735</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.195127</v>
+        <v>-0.195127</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.026735</v>
+        <v>-0.026735</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.195127</v>
+        <v>-0.195127</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MATA.xlsx
+++ b/output/pdf_financials_xlsx/MATA.xlsx
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.026735</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.195127</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.504633</v>
+        <v>3.39941</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.873823</v>
+        <v>8.725757</v>
       </c>
     </row>
     <row r="11">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.026735</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.195127</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-3.39941</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.056148</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.042843</v>
       </c>
     </row>
     <row r="13">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.611757</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.839314</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>3.911102</v>
@@ -1310,13 +1310,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.611757</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.839314</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>3.911102</v>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">

--- a/output/pdf_financials_xlsx/MATA.xlsx
+++ b/output/pdf_financials_xlsx/MATA.xlsx
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006091</v>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>0.013492</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.064514</v>
+        <v>-0.070605</v>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
@@ -5088,7 +5088,11 @@
           <t>HST Recoverable</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
